--- a/archive/2026/2026-10-21.xlsx
+++ b/archive/2026/2026-10-21.xlsx
@@ -7530,22 +7530,22 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>大成鋼</t>
         </is>
       </c>
       <c r="K23" s="7" t="n">
         <v>-735</v>
       </c>
       <c r="L23" t="n">
-        <v>450</v>
-      </c>
-      <c r="M23" s="8" t="n">
-        <v>19.5</v>
+        <v>49.9</v>
+      </c>
+      <c r="M23" s="6" t="n">
+        <v>-0.05</v>
       </c>
     </row>
     <row r="24">
@@ -7576,22 +7576,22 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>大成鋼</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="K24" s="7" t="n">
         <v>-735</v>
       </c>
       <c r="L24" t="n">
-        <v>49.9</v>
-      </c>
-      <c r="M24" s="6" t="n">
-        <v>-0.05</v>
+        <v>450</v>
+      </c>
+      <c r="M24" s="8" t="n">
+        <v>19.5</v>
       </c>
     </row>
     <row r="25">
@@ -7922,22 +7922,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>王道銀行</t>
+          <t>東和鋼鐵</t>
         </is>
       </c>
       <c r="D32" s="5" t="n">
         <v>399</v>
       </c>
       <c r="E32" t="n">
-        <v>10.9</v>
+        <v>93.3</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>0.05</v>
+        <v>2.6</v>
       </c>
       <c r="H32" t="n">
         <v>29</v>
@@ -7968,22 +7968,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2897</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>東和鋼鐵</t>
+          <t>王道銀行</t>
         </is>
       </c>
       <c r="D33" s="5" t="n">
         <v>399</v>
       </c>
       <c r="E33" t="n">
-        <v>93.3</v>
+        <v>10.9</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>2.6</v>
+        <v>0.05</v>
       </c>
       <c r="H33" t="n">
         <v>30</v>
